--- a/backup/10-09-26.xlsx
+++ b/backup/10-09-26.xlsx
@@ -64,7 +64,7 @@
     <t>Prática Clínica - Preenchimento Facial</t>
   </si>
   <si>
-    <t>Paulista</t>
+    <t>São Paulo</t>
   </si>
   <si>
     <t xml:space="preserve">Prática Clinica        </t>
